--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F50B1842-2379-4483-8997-8042D873A4EC}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8D1688-B333-40D1-BD09-8F742B0E6D68}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="152">
   <si>
     <t>Paper ID</t>
   </si>
@@ -428,6 +428,54 @@
   </si>
   <si>
     <t>Important cross-domain evidence for the human and behavioral dimensions of AI-supported decision-making. P007 strengthens the Explainability → Trust/AI Deference → Human-AI Interaction → Decision Quality part of the emerging research direction and introduces domain expertise as a potential contextual factor.</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>Emmanuel Osamuyimen Eboigbe et al.</t>
+  </si>
+  <si>
+    <t>Business Intelligence Transformation Through AI and Data Analytics</t>
+  </si>
+  <si>
+    <t>Engineering Science &amp; Technology Journal</t>
+  </si>
+  <si>
+    <t>10.51594/estj.v4i5.616</t>
+  </si>
+  <si>
+    <t>To explore the transformative impact of AI and Data Analytics on Business Intelligence, including the evolution of BI, emerging trends, practical applications, and future developments.</t>
+  </si>
+  <si>
+    <t>Systematic literature review using inclusion and exclusion criteria, structured searches, forward and backward searching, and thematic analysis.</t>
+  </si>
+  <si>
+    <t>Machine Learning, Predictive Analytics, Natural Language Processing, Deep Learning, Sentiment Analysis, Robotic Process Automation, Intelligent Automation, Augmented Analytics, Edge AI, and AI-driven data processing.</t>
+  </si>
+  <si>
+    <t>Business Intelligence, Data Analytics, Predictive Analytics, Strategic Analytics, Decision Support, and Intelligent Automation</t>
+  </si>
+  <si>
+    <t>Secondary literature including academic publications and industry reports retrieved through sources including IEEE Xplore, ScienceDirect, and Google Scholar.</t>
+  </si>
+  <si>
+    <t>AI and Data Analytics are transforming BI from traditional historical reporting toward intelligent, predictive, automated, and decision-oriented analytics. AI can improve analytical efficiency, predictive capability, insight generation, strategic planning, and accessibility of BI.</t>
+  </si>
+  <si>
+    <t>Rapid technological development may leave some emerging developments outside the review; reliance on published literature and industry reports may not capture all practical implementation experiences; the study provides broad synthesis rather than detailed empirical evaluation of individual AI algorithms.</t>
+  </si>
+  <si>
+    <t>Further research is needed on ethical AI, transparency, accountability, fairness, data privacy, user-friendly AI tools for non-technical users, and the long-term organizational impact of AI-driven BI.</t>
+  </si>
+  <si>
+    <t>Ethical AI in BI, user-friendly AI tools, AI for non-technical business users, long-term organizational impact, intelligent process automation, predictive analytics, NLP, advanced analytical modeling, and AI-supported strategic planning.</t>
+  </si>
+  <si>
+    <t>Very high. The paper directly connects AI, Data Analytics, Business Intelligence, predictive insights, and business decision-making while also highlighting organizational, human, ethical, and governance factors.</t>
+  </si>
+  <si>
+    <t>Highly relevant paper directly connecting AI and Data Analytics with BI transformation and decision support. Strengthens the technology → analytics → decision-making pathway while emphasizing skills, user engagement, strategic alignment, ethical governance, and human interpretation.</t>
   </si>
 </sst>
 </file>
@@ -570,8 +618,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S8" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A1:S8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S9" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A1:S9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="17"/>
@@ -882,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -1378,6 +1426,65 @@
         <v>135</v>
       </c>
     </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8D1688-B333-40D1-BD09-8F742B0E6D68}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC2E8B15-2140-4512-8FD4-336EE1C774C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="184">
   <si>
     <t>Paper ID</t>
   </si>
@@ -476,6 +476,102 @@
   </si>
   <si>
     <t>Highly relevant paper directly connecting AI and Data Analytics with BI transformation and decision support. Strengthens the technology → analytics → decision-making pathway while emphasizing skills, user engagement, strategic alignment, ethical governance, and human interpretation.</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>Mohamed Azmi; Abdeljebar Mansour; Chaimaa Azmi</t>
+  </si>
+  <si>
+    <t>A Context-Aware Empowering Business with AI: Case of Chatbots in Business Intelligence Systems</t>
+  </si>
+  <si>
+    <t>Procedia Computer Science, Volume 224, Pages 479–484</t>
+  </si>
+  <si>
+    <t>10.1016/j.procs.2023.09.068</t>
+  </si>
+  <si>
+    <t>To examine how Artificial Intelligence can complement and enhance Business Intelligence systems and to explore how AI-powered chatbots can support BI processes and business decision-making.</t>
+  </si>
+  <si>
+    <t>Conceptual / overview paper presenting perspectives on AI-enabled Business Intelligence and a proposed chatbot-based BI workflow. The paper discusses BI processes, compares common features of BI and AI, and presents a conceptual flowchart for chatbot-enabled BI.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Machine Learning, Natural Language Processing, AI-powered Chatbots, Predictive Analytics, Prescriptive Analytics, Anomaly Detection.</t>
+  </si>
+  <si>
+    <t>Business Intelligence, Data Analytics, Decision Support, Predictive and Prescriptive Analytics, Natural Language BI, Data Visualization.</t>
+  </si>
+  <si>
+    <t>Not applicable; conceptual paper based on existing literature and illustrative BI/chatbot processes</t>
+  </si>
+  <si>
+    <t>AI can enhance BI through automated data processing, advanced analytics, real-time analytics, predictive and prescriptive analytics, natural-language interfaces, intelligent visualization, and anomaly detection. AI-powered chatbots can improve BI accessibility, assist with queries and visualization, interpret results, provide contextual and personalized recommendations, automate routine BI tasks, and support continuous improvement through user feedback and machine learning.</t>
+  </si>
+  <si>
+    <t>The paper is primarily conceptual and does not provide a detailed empirical evaluation of chatbot-enabled BI or quantify business outcomes. Specific application areas and the measurable impact of AI-enabled BI transformation require further investigation.</t>
+  </si>
+  <si>
+    <t>Need for empirical evaluation of chatbot-enabled BI, measurement of business impact, and development and testing of optimized AI-integrated BI architectures.</t>
+  </si>
+  <si>
+    <t>Develop specific application areas and optimized BI system architectures integrating chatbots; measure the impact of AI-enabled BI transformation on relevant business activities.</t>
+  </si>
+  <si>
+    <t>Highly relevant. P009 directly connects AI, Business Intelligence, analytics, natural-language interaction, human-AI interaction, contextual insights, decision support, and business decision-making. It strengthens the emerging view that AI creates value not only through analytical capability but also through accessibility, interaction, automation, and intelligent decision support.</t>
+  </si>
+  <si>
+    <t>Strengthens the emerging research model: AI Capability → Data Processing &amp; Integration → Advanced Analytics → Predictive/Prescriptive Insights → Natural-Language Interaction → Human-AI Interaction → Decision Support → Business Decision-Making → Business Value. Adds AI-powered chatbots as an important interaction layer between AI-enabled BI systems and human decision-makers.</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>Andreas Holzinger, Anna Saranti, Christoph Molnar, Przemyslaw Biecek, Wojciech Samek</t>
+  </si>
+  <si>
+    <t>Explainable AI Methods – A Brief Overview</t>
+  </si>
+  <si>
+    <t>xxAI 2020 – Beyond Explainable AI, Lecture Notes in Artificial Intelligence (LNAI), Volume 13200, Springer, Chapter 2, pp. 13–38</t>
+  </si>
+  <si>
+    <t>10.1007/978-3-031-04083-2_2</t>
+  </si>
+  <si>
+    <t>To provide a concise overview of Explainable Artificial Intelligence methods and explain how selected XAI techniques can be used to interpret predictions of complex machine learning models, particularly for application engineers, data scientists, and beginners.</t>
+  </si>
+  <si>
+    <t>Technical overview / review of selected XAI methods. The chapter discusses 17 XAI techniques, their underlying approaches, applications, advantages, limitations, and evaluation considerations. It is not an empirical study or systematic literature review.</t>
+  </si>
+  <si>
+    <t>LIME, Anchors, GraphLIME, Layer-wise Relevance Propagation (LRP), Deep Taylor Decomposition (DTD), TCAV, XGNN, SHAP, Asymmetric Shapley Values, BreakDown, Shapley Flow, Textual Explanations of Visual Models, Integrated Gradients, Causal Models, Meaningful Perturbations, and X-NeSyL</t>
+  </si>
+  <si>
+    <t>AI-supported Business Analytics; Explainable AI; Predictive Analytics; Decision Support; Human-AI Interaction; Responsible AI</t>
+  </si>
+  <si>
+    <t>Not applicable. The chapter is a technical overview and does not introduce a single original business dataset.</t>
+  </si>
+  <si>
+    <t>XAI provides multiple approaches for interpreting complex AI and machine learning models. Explainability can support transparency, trust, acceptance, responsible AI, and decision support. Different XAI methods have different assumptions, strengths, computational requirements, and limitations. The chapter emphasizes the importance of evaluating explanation quality and moving toward causal, contextual, interactive, and human-centered explanations.</t>
+  </si>
+  <si>
+    <t>The chapter is a technical overview rather than an empirical Business Analytics study. It does not directly measure the impact of XAI on business performance or decision outcomes. The reviewed methods have different methodological and computational limitations, and some approaches require model-specific information or domain knowledge.</t>
+  </si>
+  <si>
+    <t>Need for better evaluation and measurement of explanation quality, causal and counterfactual explanations, context-aware explanations, improved human-AI interfaces, user-centered evaluation, and stronger integration of human domain expertise.</t>
+  </si>
+  <si>
+    <t>Develop XAI methods that capture causal dependencies; measure explanation quality; develop contextual human-AI interfaces; support “why,” “why not,” and “what-if” questions; improve human-in-the-loop systems; and incorporate human experience and conceptual knowledge into AI processes.</t>
+  </si>
+  <si>
+    <t>P010 strengthens the Explainability and Human-AI Interaction dimensions of the study. It provides a technical foundation for understanding how AI outputs can become more interpretable and useful for human decision-makers and supports the relationship between AI capability, analytical insight, explainability, human understanding, decision support, and business decision-making.</t>
+  </si>
+  <si>
+    <t>Book chapter / technical overview. Particularly relevant to Explainability, Transparency, Trust, Human-AI Interaction, Decision Support, Causal Reasoning, and Responsible AI. Complements P004 and P007 and provides technical foundations for the explainability-related themes emerging in the literature.</t>
   </si>
 </sst>
 </file>
@@ -618,8 +714,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S9" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A1:S9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S12" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A1:S12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="17"/>
@@ -930,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -943,7 +1039,7 @@
     <col min="8" max="8" width="178.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="255.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="130.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="57.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="137" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="124.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="255.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="229.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1485,10 +1581,129 @@
         <v>151</v>
       </c>
     </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M10" t="s">
+        <v>162</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC2E8B15-2140-4512-8FD4-336EE1C774C6}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A52B778C-EAE2-4D8F-B6A7-797E14F0F1B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="200">
   <si>
     <t>Paper ID</t>
   </si>
@@ -572,6 +572,54 @@
   </si>
   <si>
     <t>Book chapter / technical overview. Particularly relevant to Explainability, Transparency, Trust, Human-AI Interaction, Decision Support, Causal Reasoning, and Responsible AI. Complements P004 and P007 and provides technical foundations for the explainability-related themes emerging in the literature.</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>Uday Surendra Yandamuri</t>
+  </si>
+  <si>
+    <t>AI-Enabled Workflow Automation and Predictive Analytics for Enterprise Operations Management</t>
+  </si>
+  <si>
+    <t>Advances in Consumer Research, Volume 3, Issue 1, pp. 15–24</t>
+  </si>
+  <si>
+    <t>Not shown in the paper</t>
+  </si>
+  <si>
+    <t>To examine AI-enabled workflow automation and predictive analytics for enterprise operations management, including their role in decision support, operational processes, and enterprise AI implementation readiness.</t>
+  </si>
+  <si>
+    <t>Evidence-based conceptual and framework-oriented research examining AI-enabled workflow automation and predictive analytics in enterprise operations management; not presented as a conventional empirical study with a defined sample or original business dataset.</t>
+  </si>
+  <si>
+    <t>Predictive analytics; Machine Learning; Neural Networks; Decision Trees; Supervised Learning; Regression; Classification; Clustering; Natural Language Processing; Predictive Modeling; Workflow Automation; AI-enabled Decision Support</t>
+  </si>
+  <si>
+    <t>Enterprise Operations Management; Supply Chain; Inventory Management; Manufacturing; Production Planning; Quality Management; Predictive Maintenance; Finance; Accounting; Customer Service; Marketing and Sales</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>AI-enabled predictive analytics can support timely operational decision-making, while workflow automation can translate AI-supported insights into operational actions. Effective implementation depends on data quality, data integration, data lineage, data stewardship, scalable infrastructure, model validation, monitoring, human domain knowledge, organizational readiness, and change management. AI can support cost reduction, responsiveness, quality, risk management, forecasting, and operational performance improvement.</t>
+  </si>
+  <si>
+    <t>Conceptual/framework-oriented study with limited direct empirical evidence of business performance; no clearly defined original dataset or sample; implementation effectiveness depends on data quality, infrastructure, governance, model monitoring, organizational readiness, and user acceptance.</t>
+  </si>
+  <si>
+    <t>Need for stronger empirical evaluation of AI-enabled workflow automation and predictive analytics; measurement of operational performance; AI model banks; technology change management; scalable and governed AI architectures; evaluation of increasingly autonomous operational AI systems.</t>
+  </si>
+  <si>
+    <t>Future research includes operational performance evaluation, AI model banks, technology change management, improved data foundations, AI-enabled self-service operations platforms, model monitoring and feedback, and progression from AI augmentation toward self-control and full autonomy.</t>
+  </si>
+  <si>
+    <t>Strengthens the relationship between AI capability, predictive analytics, decision support, workflow automation, and operational business outcomes; adds the transition from analytical insight to operational action and highlights data governance, human expertise, organizational readiness, and change management.</t>
+  </si>
+  <si>
+    <t>Original Researcher Article; particularly relevant to AI-enabled Operations Management, Predictive Analytics, Workflow Automation, Decision Support, Data Governance, Operational Performance, Human Expertise, Organizational Readiness, and AI Autonomy.</t>
   </si>
 </sst>
 </file>
@@ -714,8 +762,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S12" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A1:S12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S13" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A1:S13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="17"/>
@@ -1026,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -1699,6 +1747,65 @@
         <v>183</v>
       </c>
     </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A52B778C-EAE2-4D8F-B6A7-797E14F0F1B4}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB8B76F5-EFF1-49DB-BE45-A592F3965B43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="216">
   <si>
     <t>Paper ID</t>
   </si>
@@ -620,6 +620,54 @@
   </si>
   <si>
     <t>Original Researcher Article; particularly relevant to AI-enabled Operations Management, Predictive Analytics, Workflow Automation, Decision Support, Data Governance, Operational Performance, Human Expertise, Organizational Readiness, and AI Autonomy.</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>Jing Xue, Guo Li, Dmitry Ivanov</t>
+  </si>
+  <si>
+    <t>Digital transformation in the blockchain era: Balancing efficiency and resilience in operations management</t>
+  </si>
+  <si>
+    <t>International Journal of Production Economics</t>
+  </si>
+  <si>
+    <t>10.1016/j.ijpe.2025.109525</t>
+  </si>
+  <si>
+    <t>To examine how digital transformation affects corporate innovation and how resource-allocation efficiency, organizational resilience, information transparency, and market competition influence this relationship.</t>
+  </si>
+  <si>
+    <t>Quantitative empirical study using panel data, two-way fixed-effects models, robustness tests, instrumental-variable analysis, moderation analysis, and mediation analysis.</t>
+  </si>
+  <si>
+    <t>AI and other digital technologies, including big data, cloud computing, blockchain, and digital technology applications. The study examines digital transformation broadly rather than evaluating a specific AI model.</t>
+  </si>
+  <si>
+    <t>Operations Management, Supply Chain Management, Digital Transformation, Resource Allocation, Organizational Resilience, and Corporate Innovation.</t>
+  </si>
+  <si>
+    <t>Chinese A-share listed companies, 2010–2020; 20,552 firm-year observations covering 3,261 companies. Data sources include CSMAR, Wind, PatSnap, and corporate annual reports.</t>
+  </si>
+  <si>
+    <t>Digital transformation is associated with improvements in corporate innovation quantity and quality, resource-allocation efficiency, and organizational resilience. Information transparency strengthens the positive relationship between digital transformation and innovation, while market competition weakens it in the study. The effects of combining technologies are not always positive.</t>
+  </si>
+  <si>
+    <t>The study focuses on Chinese listed companies, limiting the direct generalization of findings to SMEs and other countries. It examines corporate innovation and related organizational outcomes rather than directly measuring managerial decision quality.</t>
+  </si>
+  <si>
+    <t>The direct relationship between digital transformation and decision quality, as well as its applicability to SMEs and other business contexts, requires further investigation.</t>
+  </si>
+  <si>
+    <t>Examine SMEs and operational changes driven by digital transformation. Further review-level opportunities include studying how technology combinations affect operational performance and decision-making across industries and countries.</t>
+  </si>
+  <si>
+    <t>Provides supporting evidence that AI and broader digital capabilities can contribute to business outcomes through resource-allocation efficiency and organizational resilience. It supports the operational-outcomes part of our review but does not directly establish that AI improves managerial decision quality.</t>
+  </si>
+  <si>
+    <t>Empirical study based on Chinese listed companies. Digital transformation is broader than AI alone. Do not treat the findings as direct evidence of improved managerial decision quality.</t>
   </si>
 </sst>
 </file>
@@ -762,8 +810,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S13" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A1:S13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S14" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A1:S14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="17"/>
@@ -1074,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -1806,6 +1854,65 @@
         <v>199</v>
       </c>
     </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB8B76F5-EFF1-49DB-BE45-A592F3965B43}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E8F8D6-D7D1-432D-8F3E-AABD6E375F5D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="232">
   <si>
     <t>Paper ID</t>
   </si>
@@ -668,6 +668,54 @@
   </si>
   <si>
     <t>Empirical study based on Chinese listed companies. Digital transformation is broader than AI alone. Do not treat the findings as direct evidence of improved managerial decision quality.</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t>Safae Bakhouch, Brahim Benbba</t>
+  </si>
+  <si>
+    <t>A comprehensive review of competency models for 3PL operations managers: Bibliometric and systematic analysis</t>
+  </si>
+  <si>
+    <t>The Asian Journal of Shipping and Logistics</t>
+  </si>
+  <si>
+    <t>10.1016/j.ajsl.2025.11.001</t>
+  </si>
+  <si>
+    <t>To examine existing competency models in logistics and supply chain management, identify the technical, managerial, digital, and interpersonal competencies required by third-party logistics operations managers, and propose an integrated competency framework.</t>
+  </si>
+  <si>
+    <t>Bibliometric analysis and systematic literature review using Scopus and PRISMA 2020 screening, bibliometric mapping with VOSviewer, qualitative content analysis using NVivo 14, and a qualitative empirical investigation involving semi-structured interviews and participant observation.</t>
+  </si>
+  <si>
+    <t>AI is discussed as an emerging logistics technology and digital competency area. The paper does not experimentally evaluate a specific AI algorithm or model.</t>
+  </si>
+  <si>
+    <t>Logistics Management, Supply Chain Management, Third-Party Logistics, Digital Competencies, Data Analytics, Operations Management, and Decision-Making.</t>
+  </si>
+  <si>
+    <t>Scopus literature covering 1995–2024; 24 selected sources for content analysis; qualitative interviews and participant observation involving experienced 3PL operations managers in the Tangier–Tetouan–Al Hoceima region of Morocco.</t>
+  </si>
+  <si>
+    <t>Existing competency models can be too generic and may lack detailed technical requirements for 3PL operations managers. Digital competencies involving AI, IoT, big data analytics, and digital logistics systems are increasingly important. The proposed framework groups competencies into four categories: technical, procedural, transversal, and linguistic. Continuous learning, communication, adaptability, leadership, and data-driven decision-making are also important.</t>
+  </si>
+  <si>
+    <t>Existing models have gaps in technical specificity, contextual relevance, international and cross-cultural perspectives, digital competencies, and sustainability competencies. The proposed framework would benefit from further validation in different organizational and geographical contexts.</t>
+  </si>
+  <si>
+    <t>The need for practical and context-specific competency frameworks for 3PL operations managers, including better integration of digital competencies and stronger evidence linking individual competencies to operational performance.</t>
+  </si>
+  <si>
+    <t>Study the effects of emerging technologies such as AI and blockchain; develop and validate competency-assessment tools; align educational curricula with industry requirements; investigate relationships between competencies and operational performance; and validate the framework across different contexts.</t>
+  </si>
+  <si>
+    <t>Highlights human competencies, digital skills, and organizational readiness as factors that may influence effective use of analytics and digital technologies. It provides supporting context for our review but does not directly establish that AI improves managerial decision quality.</t>
+  </si>
+  <si>
+    <t>Bibliometric and systematic review combined with qualitative empirical investigation. Figure 6 on page 10 presents the proposed four-category competency framework. Treat this as supporting evidence about human and organizational capabilities rather than direct evidence of AI-driven decision-quality improvement.</t>
   </si>
 </sst>
 </file>
@@ -810,8 +858,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S14" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A1:S14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S15" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A1:S15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="17"/>
@@ -1122,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -1913,6 +1961,65 @@
         <v>215</v>
       </c>
     </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E8F8D6-D7D1-432D-8F3E-AABD6E375F5D}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327652E8-6A6C-4685-9421-C045241A0B66}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="248">
   <si>
     <t>Paper ID</t>
   </si>
@@ -716,6 +716,54 @@
   </si>
   <si>
     <t>Bibliometric and systematic review combined with qualitative empirical investigation. Figure 6 on page 10 presents the proposed four-category competency framework. Treat this as supporting evidence about human and organizational capabilities rather than direct evidence of AI-driven decision-quality improvement.</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>Jackson, Ilya; Ivanov, Dmitry; Dolgui, Alexandre; Namdar, Jafar</t>
+  </si>
+  <si>
+    <t>Generative Artificial Intelligence in Supply Chain and Operations Management: A Capability-Based Framework for Analysis and Implementation</t>
+  </si>
+  <si>
+    <t>International Journal of Production Research</t>
+  </si>
+  <si>
+    <t>10.1080/00207543.2024.2309309</t>
+  </si>
+  <si>
+    <t>To develop a capability-based framework explaining how AI and generative AI can be applied across supply chain and operations management decision-making areas.</t>
+  </si>
+  <si>
+    <t>Conceptual framework development using selected literature and application examples; Resource-Based View (RBV).</t>
+  </si>
+  <si>
+    <t>AI capabilities: learning, perception, prediction, interaction, adaptation, and reasoning; generative AI and creativity-related capabilities.</t>
+  </si>
+  <si>
+    <t>Supply chain management, operations management, forecasting, inventory, production planning, scheduling, routing, and risk management.</t>
+  </si>
+  <si>
+    <t>Selected examples from existing research and industry applications; no single new empirical dataset.</t>
+  </si>
+  <si>
+    <t>Proposes a framework linking AI capabilities to 13 supply chain and operations management decision areas. Generative AI extends AI capabilities through content and scenario generation, interaction, and decision support. AI may complement human expertise and organisational resources.</t>
+  </si>
+  <si>
+    <t>Not an exhaustive literature review; relies on selected examples; framework requires further refinement and empirical validation.</t>
+  </si>
+  <si>
+    <t>Need for comprehensive reviews, more granular operational categories, and empirical evidence assessing AI and generative AI outcomes across decision-making contexts.</t>
+  </si>
+  <si>
+    <t>Conduct comprehensive literature reviews; refine framework categories; investigate broader Industry 4.0 and Industry 5.0 applications and human-machine collaboration.</t>
+  </si>
+  <si>
+    <t>Provides a capability-based explanation of how AI supports analytics and operational decision-making; conceptual support rather than direct empirical proof of improved decision quality.</t>
+  </si>
+  <si>
+    <t>Conceptual framework-development study grounded in RBV. Do not interpret it as direct causal evidence that AI improves decision quality.</t>
   </si>
 </sst>
 </file>
@@ -762,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -773,70 +821,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -858,28 +909,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S15" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S15" headerRowDxfId="21" dataDxfId="0" totalsRowDxfId="20">
   <autoFilter ref="A1:S15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Year" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Paper Title" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Journal / Conference" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Quartile (Q1/Q2/Q3/Q4)" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DOI" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Research Objective" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Research Methodology" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="AI Technique" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Business Analytics Domain" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Dataset / Data Source" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Key Findings" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Limitations" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Research Gap" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Future Research" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Relevance to Our Study" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Review Status" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Year" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Paper Title" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Journal / Conference" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Quartile (Q1/Q2/Q3/Q4)" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DOI" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Research Objective" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Research Methodology" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="AI Technique" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Business Analytics Domain" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Dataset / Data Source" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Key Findings" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Limitations" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Research Gap" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Future Research" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Relevance to Our Study" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Review Status" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Notes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1170,27 +1221,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
     <col min="2" max="2" width="106" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="2" customWidth="1"/>
-    <col min="4" max="4" width="114.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="114.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="57.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="178.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="255.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="130.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="178.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="255.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="130.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="137" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="124.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="255.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="229.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="227.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="240.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="255.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="229.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="227.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="240.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="2" customWidth="1"/>
-    <col min="19" max="19" width="212.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="212.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -1254,770 +1305,829 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>2026</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>2026</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="S4" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>2026</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="S5" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>2025</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>2025</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="S7" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>2026</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="R8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>2023</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="R9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>2023</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="R10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="S10" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>2022</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q11" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="R11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="S11" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>2026</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="P12" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="Q12" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="R12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="S12" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>2025</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="P13" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="Q13" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="R13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="S13" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>2026</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="O14" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="P14" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="Q14" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="R14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="S14" s="3" t="s">
         <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/Literature_Matrix_Template.xlsx
+++ b/Literature_Matrix_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d72ec21f11f23aa/Desktop/Reasearch Work - GitHub and LinkedIn/AI_Business_Analytics_Research/02-Literature_Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327652E8-6A6C-4685-9421-C045241A0B66}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{961A7E3A-8450-4A1E-B59B-587B694A24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4D6B24-25BF-4051-A553-88896203B9D9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="264">
   <si>
     <t>Paper ID</t>
   </si>
@@ -764,6 +764,54 @@
   </si>
   <si>
     <t>Conceptual framework-development study grounded in RBV. Do not interpret it as direct causal evidence that AI improves decision quality.</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>Jin, Rui; Liu, Qihao; Li, Xinyu; Gao, Liang</t>
+  </si>
+  <si>
+    <t>Scheduling for Remanufacturing Systems with Finite Buffers: A Regional Co-Evolutionary Algorithm Integrating Deadlock Repair Mechanism</t>
+  </si>
+  <si>
+    <t>Chinese Journal of Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>10.1016/j.cjme.2026.100408</t>
+  </si>
+  <si>
+    <t>To develop a mathematical model and optimisation algorithm for integrated remanufacturing scheduling under finite-buffer constraints, minimising makespan and workload imbalance while preventing deadlocks.</t>
+  </si>
+  <si>
+    <t>Quantitative computational optimisation study involving mathematical modelling, OR-Tools model validation, development of KERCEA, and comparative experiments across 36 test instances. Each algorithm-instance experiment was repeated 20 times, with benchmark comparisons and ablation studies.</t>
+  </si>
+  <si>
+    <t>Knowledge-enhanced regional co-evolutionary algorithm (KERCEA), evolutionary optimisation, heuristic initialisation, multi-objective search, and deadlock detection and repair.</t>
+  </si>
+  <si>
+    <t>Operations analytics, manufacturing optimisation, production scheduling, resource allocation, workload balancing, and sustainable remanufacturing.</t>
+  </si>
+  <si>
+    <t>36 computational test instances representing different remanufacturing system sizes; no primary real-world organisational dataset reported.</t>
+  </si>
+  <si>
+    <t>KERCEA outperformed five benchmark algorithms on reported optimisation metrics. It improved solution quality, diversity, and convergence and reduced average blocking time on four representative instances by 13.68%, 4.13%, 62.01%, and 11.94%, respectively, relative to the best-performing benchmark in each instance.</t>
+  </si>
+  <si>
+    <t>Assumes deterministic processing times and stable workstation availability; excludes random machine failures and certain operational overheads. Evaluation relies on computational test instances rather than a reported real-world industrial deployment.</t>
+  </si>
+  <si>
+    <t>Need to incorporate operational uncertainty, including uncertain processing times and random machine failures, and improve the realism of scheduling models. The paper does not directly examine managerial decision quality or wider business analytics adoption.</t>
+  </si>
+  <si>
+    <t>Extend the model to incorporate stochastic dynamics, uncertain processing times, and random machine failures.</t>
+  </si>
+  <si>
+    <t>Provides indirect supporting evidence on algorithmic optimisation for operational decision support. Its focus is manufacturing scheduling rather than broader AI-enabled business analytics or managerial decision-making.</t>
+  </si>
+  <si>
+    <t>Quantitative computational optimisation study. Do not treat its results as direct evidence that AI improves general managerial decision quality. The uploaded article is a journal pre-proof, not the definitive Version of Record.</t>
   </si>
 </sst>
 </file>
@@ -810,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -822,7 +870,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,64 +884,64 @@
   </cellStyles>
   <dxfs count="22">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -909,8 +963,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S15" headerRowDxfId="21" dataDxfId="0" totalsRowDxfId="20">
-  <autoFilter ref="A1:S15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrix" displayName="LiteratureMatrix" ref="A1:S17" headerRowDxfId="21" dataDxfId="0" totalsRowDxfId="20">
+  <autoFilter ref="A1:S17" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper ID" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors" dataDxfId="18"/>
@@ -1221,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -1305,830 +1359,910 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>2026</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>2026</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>2026</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>2025</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="R6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>2025</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="P7" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="Q7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="R7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="S7" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>2026</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="Q8" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>2023</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="Q9" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="R9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>2023</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="O10" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="P10" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="R10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10" s="4" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>2022</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="O11" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="P11" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="Q11" s="3" t="s">
+      <c r="Q11" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="R11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>2026</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L12" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N12" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="O12" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="P12" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="Q12" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="R12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="S12" s="4" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <v>2025</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="L13" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M13" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N13" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="O13" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="P13" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="Q13" s="3" t="s">
+      <c r="Q13" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="R13" s="3" t="s">
+      <c r="R13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="S13" s="4" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>2026</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="O14" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="P14" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="4" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>2024</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="P15" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q15" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="4" t="s">
         <v>247</v>
       </c>
+    </row>
+    <row r="16" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
